--- a/Valuation Project_V01150965_Dollar General.xlsx
+++ b/Valuation Project_V01150965_Dollar General.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c5703df471173b21/college/VCU/Cases in financial mgt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1407" documentId="8_{A05F9995-BEE5-ED49-8782-A1BAC4349D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D429A2A1-0D1D-8F49-A862-7844E4041A68}"/>
+  <xr:revisionPtr revIDLastSave="1408" documentId="8_{A05F9995-BEE5-ED49-8782-A1BAC4349D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD0FC00E-879F-9B4E-AC74-8ECE08EB413B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{DBCCEA9E-397B-3646-87B4-C771944BAA10}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16360" xr2:uid="{DBCCEA9E-397B-3646-87B4-C771944BAA10}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparables" sheetId="1" r:id="rId1"/>
@@ -958,6 +958,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -972,9 +975,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4335,16 +4335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="E1" s="86" t="s">
+      <c r="E1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86" t="s">
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="86"/>
+      <c r="J1" s="87"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -4392,11 +4392,11 @@
       <c r="O2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="90" t="s">
+      <c r="Q2" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="90"/>
-      <c r="S2" s="90"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
@@ -4755,22 +4755,22 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="D12" s="85" t="s">
+      <c r="B12" s="86"/>
+      <c r="D12" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="G12" s="85" t="s">
+      <c r="E12" s="86"/>
+      <c r="G12" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="85"/>
-      <c r="J12" s="85" t="s">
+      <c r="H12" s="86"/>
+      <c r="J12" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="K12" s="85"/>
+      <c r="K12" s="86"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -4878,22 +4878,22 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="D18" s="85" t="s">
+      <c r="B18" s="86"/>
+      <c r="D18" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="85"/>
-      <c r="G18" s="85" t="s">
+      <c r="E18" s="86"/>
+      <c r="G18" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="85"/>
-      <c r="J18" s="85" t="s">
+      <c r="H18" s="86"/>
+      <c r="J18" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="85"/>
+      <c r="K18" s="86"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
@@ -4986,17 +4986,17 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="87">
+      <c r="B24" s="88">
         <f>DCF_baseline!G4</f>
         <v>42033.738779999992</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="89"/>
-      <c r="B25" s="88"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="89"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="20" t="s">
@@ -5007,22 +5007,22 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="85"/>
-      <c r="D28" s="85" t="s">
+      <c r="B28" s="86"/>
+      <c r="D28" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="85"/>
-      <c r="G28" s="85" t="s">
+      <c r="E28" s="86"/>
+      <c r="G28" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="85"/>
-      <c r="J28" s="85" t="s">
+      <c r="H28" s="86"/>
+      <c r="J28" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="K28" s="85"/>
+      <c r="K28" s="86"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
@@ -5120,22 +5120,22 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="85"/>
-      <c r="D34" s="85" t="s">
+      <c r="B34" s="86"/>
+      <c r="D34" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="85"/>
-      <c r="G34" s="85" t="s">
+      <c r="E34" s="86"/>
+      <c r="G34" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="85"/>
-      <c r="J34" s="85" t="s">
+      <c r="H34" s="86"/>
+      <c r="J34" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="K34" s="85"/>
+      <c r="K34" s="86"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
@@ -5229,11 +5229,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="G34:H34"/>
@@ -5250,6 +5245,11 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="J28:K28"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7995,7 +7995,8 @@
     <col min="1" max="1" width="26.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="11.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
